--- a/RF3/RepDays-K-medoids_dtw.xlsx
+++ b/RF3/RepDays-K-medoids_dtw.xlsx
@@ -442,42 +442,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>355</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1287671232876712</v>
+        <v>0.2767123287671233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.1315068493150685</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1123287671232877</v>
+        <v>0.09315068493150686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1726027397260274</v>
+        <v>0.136986301369863</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2301369863013699</v>
+        <v>0.3616438356164384</v>
       </c>
     </row>
   </sheetData>
